--- a/data/trans_dic/P39A1_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P39A1_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar, mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar, mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 90,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>69,87; 84,4</t>
+          <t>69,35; 84,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>69,01; 82,11</t>
+          <t>68,61; 82,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72,29; 81,88</t>
+          <t>71,69; 81,76</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>65,69; 76,93</t>
+          <t>65,0; 76,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,56; 71,61</t>
+          <t>34,37; 71,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47,93; 71,8</t>
+          <t>46,6; 71,71</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66,55; 75,03</t>
+          <t>66,8; 74,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,91; 67,89</t>
+          <t>61,53; 68,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65,22; 70,48</t>
+          <t>65,23; 70,6</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>67,99; 90,3</t>
+          <t>67,77; 91,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60,36; 66,43</t>
+          <t>60,3; 66,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65,19; 81,52</t>
+          <t>65,58; 83,28</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>65,63; 73,39</t>
+          <t>66,18; 73,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,59; 74,23</t>
+          <t>68,45; 74,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68,09; 72,92</t>
+          <t>67,94; 72,74</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>64,3; 72,52</t>
+          <t>64,11; 72,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69,51; 93,78</t>
+          <t>69,51; 93,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69,07; 89,83</t>
+          <t>68,8; 87,69</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>66,19; 75,89</t>
+          <t>66,39; 76,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>62,73; 70,43</t>
+          <t>62,5; 69,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>65,44; 70,99</t>
+          <t>65,18; 71,19</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>70,24; 80,19</t>
+          <t>70,44; 79,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>65,0; 74,24</t>
+          <t>64,76; 74,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68,27; 74,97</t>
+          <t>68,32; 75,12</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar, mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar, mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 90,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>248849; 300577</t>
+          <t>246986; 299337</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>189281; 225187</t>
+          <t>188165; 225241</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>455718; 516169</t>
+          <t>451957; 515406</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>256304; 300169</t>
+          <t>253610; 299305</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>170384; 343162</t>
+          <t>164677; 341972</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>416693; 624168</t>
+          <t>405128; 623402</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>342560; 386232</t>
+          <t>343844; 383960</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>311493; 347188</t>
+          <t>314637; 350994</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>669249; 723235</t>
+          <t>669343; 724396</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>571779; 759419</t>
+          <t>569892; 767539</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>382422; 420894</t>
+          <t>382041; 420256</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>961232; 1202037</t>
+          <t>966973; 1228031</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>344479; 385196</t>
+          <t>347380; 386503</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>342932; 371132</t>
+          <t>342242; 371958</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>697847; 747303</t>
+          <t>696257; 745450</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>213904; 241273</t>
+          <t>213280; 241241</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>396070; 534364</t>
+          <t>396075; 530893</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>623308; 810728</t>
+          <t>620864; 791373</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>156735; 179710</t>
+          <t>157217; 180692</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>209892; 235649</t>
+          <t>209111; 233913</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>373891; 405609</t>
+          <t>372416; 406745</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2245141; 2563337</t>
+          <t>2251465; 2526047</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2146870; 2451928</t>
+          <t>2138889; 2451416</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4437255; 4872637</t>
+          <t>4440457; 4882168</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P39A1_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P39A1_2023-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>76,35%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>69,35; 84,05</t>
+          <t>69,76; 84,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68,61; 82,13</t>
+          <t>68,6; 81,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71,69; 81,76</t>
+          <t>70,63; 80,51</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>70,4%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>65,0; 76,71</t>
+          <t>65,23; 76,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,37; 71,37</t>
+          <t>65,18; 74,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46,6; 71,71</t>
+          <t>66,78; 73,88</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,34%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66,8; 74,59</t>
+          <t>66,44; 74,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61,53; 68,64</t>
+          <t>60,63; 67,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65,23; 70,6</t>
+          <t>64,75; 69,6</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>67,1%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>67,77; 91,27</t>
+          <t>66,11; 73,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60,3; 66,33</t>
+          <t>61,48; 67,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65,58; 83,28</t>
+          <t>64,73; 69,19</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,02%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,18; 73,63</t>
+          <t>65,89; 72,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,45; 74,39</t>
+          <t>67,51; 73,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67,94; 72,74</t>
+          <t>67,68; 72,37</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>69,99%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>64,11; 72,51</t>
+          <t>64,66; 73,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69,51; 93,17</t>
+          <t>67,74; 74,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68,8; 87,69</t>
+          <t>67,31; 72,51</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,13%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>66,39; 76,31</t>
+          <t>66,38; 75,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>62,5; 69,91</t>
+          <t>62,2; 69,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>65,18; 71,19</t>
+          <t>65,19; 70,82</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>69,47%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>70,44; 79,03</t>
+          <t>69,08; 72,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>64,76; 74,22</t>
+          <t>66,72; 69,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68,32; 75,12</t>
+          <t>68,31; 70,5</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>276828</t>
+          <t>272698</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>208810</t>
+          <t>243277</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>485638</t>
+          <t>515975</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>246986; 299337</t>
+          <t>247632; 299606</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>188165; 225241</t>
+          <t>220083; 261747</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>451957; 515406</t>
+          <t>477294; 544108</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>278646</t>
+          <t>312630</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>285738</t>
+          <t>317029</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>564385</t>
+          <t>629659</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>253610; 299305</t>
+          <t>286242; 335636</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>164677; 341972</t>
+          <t>296970; 337160</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>405128; 623402</t>
+          <t>597320; 660779</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>365218</t>
+          <t>408926</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>331675</t>
+          <t>373134</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>696893</t>
+          <t>782060</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>343844; 383960</t>
+          <t>385518; 429916</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>314637; 350994</t>
+          <t>352288; 390719</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>669343; 724396</t>
+          <t>751928; 808266</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>657480</t>
+          <t>450100</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>402259</t>
+          <t>441908</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1059739</t>
+          <t>892008</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>569892; 767539</t>
+          <t>425001; 473896</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>382041; 420256</t>
+          <t>422096; 460044</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>966973; 1228031</t>
+          <t>860523; 919836</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>365777</t>
+          <t>392371</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>357419</t>
+          <t>392041</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>723196</t>
+          <t>784412</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>347380; 386503</t>
+          <t>373199; 412961</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>342242; 371958</t>
+          <t>373986; 407927</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>696257; 745450</t>
+          <t>758187; 810767</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>228203</t>
+          <t>252661</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>462934</t>
+          <t>283139</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>691137</t>
+          <t>535799</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>213280; 241241</t>
+          <t>237193; 268187</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>396075; 530893</t>
+          <t>270065; 296714</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>620864; 791373</t>
+          <t>515318; 555077</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>168844</t>
+          <t>184915</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>222322</t>
+          <t>242148</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>391167</t>
+          <t>427063</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>157217; 180692</t>
+          <t>172457; 196568</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>209111; 233913</t>
+          <t>228290; 254350</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>372416; 406745</t>
+          <t>408627; 443892</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2340996</t>
+          <t>2274301</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2271157</t>
+          <t>2292676</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4612153</t>
+          <t>4566977</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2251465; 2526047</t>
+          <t>2217596; 2329826</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2138889; 2451416</t>
+          <t>2244329; 2337865</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4440457; 4882168</t>
+          <t>4490424; 4634367</t>
         </is>
       </c>
     </row>
